--- a/Result/checksun_type/感測裝置.xlsx
+++ b/Result/checksun_type/感測裝置.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>180.1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>192.48</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>204.15</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>192.48</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>204.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>36943.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>39836.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>39836.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>50326.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>65996.78</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>65996.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-4742.652726969813</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>36943</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>36943.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>178.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>193.4</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>204.62</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>204.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>33482.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>39677.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>39677.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>52291.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>65946.1</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>65946.10000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-4340.076928382987</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>33482</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>33482.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>178.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>194.22</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>205.25</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>194.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>205.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>48660.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>48462.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>48462.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>54012.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>66227.04</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>66227.03999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3239.144468673854</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>48660</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>48660.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>180.7</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>195.7</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>206.08</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>206.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>42051.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>54882.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>54882</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>59258.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>67551.82</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>67551.82000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-3176.914366636738</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>42051</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>42051.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>185.7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>197.32</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>206.93</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>197.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>206.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>38048.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>57726.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>57726</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>69450.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>69283.68</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>69283.67999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-2266.445850632386</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>38048</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>38048.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>189.4</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>198.65</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>207.37</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>198.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>207.37</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>36147.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>60816.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>60816.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>72102.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>69276.46</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>69276.46000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-455.9391902464558</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>36147</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>36147.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>193.4</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>200.18</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>207.83</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>200.18</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>207.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>77407.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>64905.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>64905.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>74063.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>69236.24</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>69236.24000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>2350.461009956533</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>77407</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>77407.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>197.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>201.58</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>208.31</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>201.58</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>208.31</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>80757.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>59563.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>59563</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>71329.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>68435.4</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>68435.39999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>1854.944831319503</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>80757</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>80757.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>198.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>202.52</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>208.58</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>202.52</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>208.58</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>56271.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>63635.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>63635.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>71618.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>67586.4</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>67586.39999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>721.8879750052001</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>56271</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>56271.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>197.9</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>203.45</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>208.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>203.45</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>208.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>53499.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>81174.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>81174</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>69622.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>68217.18</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>68217.17999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>1700.95360973457</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>53499</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>53499.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>199.2</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>204.2</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>208.74</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>204.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>208.74</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>56593.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>83388.8</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>83388.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>68162.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>68194.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>68194.74000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>3335.870459000304</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>56593</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>56593.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>76.6</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>76.74</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>72.7</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>10866.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>22805.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>22805.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>24824.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>35440.92</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>35440.92</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3885.075831923583</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>10866</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>10866.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>77.14</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>72.47</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>72.47</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>17378.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>27706.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>27706.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>24765.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>35335.7</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>35335.7</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3149.155131571762</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>17378</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>17378.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>77.26</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>77.32</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>72.23</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.23</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>15223.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>29440.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>29440.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>24659.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>35124.82</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>35124.82</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2683.0843049416</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>15223</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>15223.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>76.78</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>77.34</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>71.99</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.98999999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>45420.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>33913.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>33913.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>24919.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>35385.58</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>35385.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1690.551541722016</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>45420</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>45420.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>76.18</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>77.04</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>71.74</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>71.73999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>25142.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>29029.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>29029</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>22596.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>34755.56</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>34755.56</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3447.66361063255</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>25142</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>25142.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>75.36</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>76.87</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>71.49</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>71.48999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>35370.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>26843.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>26843</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>22428.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>34604.28</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>34604.28</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-3662.050008696431</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>35370</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>35370.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>75.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>76.91</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>71.23999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>26048.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>21824.8</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>21824.8</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>20128.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>34252.9</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>34252.9</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-4933.385934191385</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>26048</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>26048.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>74.91999999999999</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>77.08</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>70.95</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>70.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>37589.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>19878.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>19878.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>19679.1</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>33981.94</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>33981.94</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-5574.602044391628</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>37589</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>37589.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>75.1</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>76.96</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>70.72</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>70.72</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>20996.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>15926.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>15926</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>18147.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>34130.62</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>34130.62</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-7528.067843092274</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>20996</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>20996.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>75.72</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>70.42</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>70.42</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>14212.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>16164.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>16164.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>20662.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>33992.8</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>33992.8</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-8272.052275411334</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>14212</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>14212.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>76.24000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>70.11</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>70.11</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>10279.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>18013.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>18013.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>25789.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>33780.52</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>33780.52</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-8312.599597459583</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>10279</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>10279.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>80.32000000000001</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>83.28</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>83.76</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>83.28</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>83.76000000000001</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>6154.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>11416.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>11416</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>14200.7</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>19092.5</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>19092.5</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-2276.381225536164</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>6154</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>6154.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>79.82</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>83.32</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>83.95</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>83.95</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>7843.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>13837.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>13837.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>17431.8</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>19372.7</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>19372.7</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1847.58152362209</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>7843</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>7843.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>79.88</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>83.48</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>84.18</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>83.48</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>84.18000000000001</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>9429.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>17352.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>17352.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>19005.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>19449.8</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>19449.8</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1349.98975218691</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>9429</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>9429.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>80.98</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>83.71</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>84.41</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>84.41</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>12303.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>17354.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>17354</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>19326.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>19488.74</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>19488.74</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-760.8590161299762</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>12303</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>12303.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>81.96000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>84.68</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>84.68000000000001</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>21351.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>17917.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>17917.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>19846.7</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>19569.2</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>19569.2</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-199.9987140439989</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>21351</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>21351.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>82.96000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>84.3</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>84.92</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>84.92</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>18262.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>16985.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>16985.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>20408.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>19515.22</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>19515.22</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-361.055471276748</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>18262</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>18262.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>84.48</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>84.84</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>85.2</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>84.84</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>85.2</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>25418.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>21026.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>21026</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>22200.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>20361.92</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>20361.92</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-247.277429063648</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>25418</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>25418.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>85.7</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>85.18</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>85.47</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>85.47</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>9436.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>20658.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>20658.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>22253.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>20413.76</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>20413.76</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-842.6203177212301</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>9436</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>9436.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>85.22</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>85.06</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>85.63</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>85.63</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>15121.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>21299.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>21299.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>23448.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21080.66</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21080.66</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>49.34056697226697</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>15121</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>15121.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>85.38</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>85.1</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>85.8</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>85.8</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>16690.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>21775.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>21775.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>23259.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>21155.18</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>21155.18</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>712.7010962853965</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>16690</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>16690.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>85.42</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>84.87</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>85.95</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>85.95</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>38465.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>23831.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>23831</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>22246.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>21400.92</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>21400.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>1466.798241865392</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>38465</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>38465.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>203.0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>217.92</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>246990.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>261303.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>261303.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>360072.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>1087687.9</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>1087687.9</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-60756.27700912725</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>246990</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>246990.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>219.42</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>229.64</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>229.64</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>188584.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>277235.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>277235.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>364259.9</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>1109012.44</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>1109012.44</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-62901.108610934</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>188584</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>188584.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>200.9</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>229.9</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>229.9</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>266834.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>327128.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>327128.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>378625.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>1132112.48</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>1132112.48</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-57460.89987741027</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>266834</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>266834.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>230.31</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>230.31</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>328496.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>351582.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>351582.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>393659.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>1170503.62</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>1170503.62</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-56020.92669104022</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>328496</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>225.2</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>230.45</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>230.45</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>275614.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>419383.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>419383</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>399217.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>1181679.14</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>1181679.14</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-58569.71761440305</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>275614</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>209.8</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>230.35</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>326648.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>458840.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>458840.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>399885.8</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>1187183.2</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>1187183.2</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-54453.1433044069</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>326648</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>214.9</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>229.28</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>230.34</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>230.34</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>438050.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>451284.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>451284.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>403006.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>1190565.96</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>1190565.96</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-52095.49631496938</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>438050</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>219.1</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>230.29</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>230.29</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>389105.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>430123.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>430123.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>398138.1</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1191948.4</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1191948.4</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-58802.80431880965</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>389105</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>232.15</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>229.96</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>232.15</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>229.96</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>667498.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>435737.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>435737</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>393344.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1189336.42</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1189336.42</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-61040.46559862403</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>667498</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>233.28</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>472903.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>379052.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>379052.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>373683.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1181965.28</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1181965.28</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-91884.92936983652</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>472903</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>233.52</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>229.07</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>229.07</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>288867.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>340930.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>340930.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>402140.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1178670.4</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1178670.4</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-111817.3801369317</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>288867</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20055,11 +19791,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
           <t>2459</t>
@@ -20241,41 +19973,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr">
         <is>
           <t>0</t>
@@ -20296,20 +20024,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20050,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>0</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20219,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20403,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>26.01</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20454,16 @@
           <t>69398365.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>46175655.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>46175655.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>40727993.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>194676121.56</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>194676121.56</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20480,10 @@
           <t>-6011750.455637693</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>69398365</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>69398365.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20649,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20833,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20884,16 @@
           <t>40606624.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>40014316.2</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>40014316.2</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>41687883.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>195169236.84</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>195169236.84</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20910,10 @@
           <t>-9065902.528399438</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>40606624</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>40606624.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21079,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21263,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>25.97</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21314,16 @@
           <t>33681849.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>39637812.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>39637812.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>51965661.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>195984000.1</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>195984000.1</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21340,10 @@
           <t>-10020365.29204483</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>33681849</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>33681849.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21693,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21744,16 @@
           <t>49106509.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>38566967.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>38566967.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>52615128.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>195992723.02</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>195992723.02</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21770,10 @@
           <t>-10284073.15825091</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>49106509</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>49106509.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21939,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22123,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22174,16 @@
           <t>38084932.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>35331650.4</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>35331650.4</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>52705529.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>195762947.24</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>195762947.24</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22200,10 @@
           <t>-11946152.49717921</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>38084932</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>38084932.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22369,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22553,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>25.95</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22604,16 @@
           <t>38591667.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>35280331.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>35280331.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>51774555.3</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>196053683.56</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>196053683.56</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22630,10 @@
           <t>-12713019.99932038</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>38591667</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>38591667.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22799,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22983,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23034,16 @@
           <t>38724107.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>43361451.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>43361451.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>53384515.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>197488634.64</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>197488634.64</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23060,10 @@
           <t>-13408801.60954632</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>38724107</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>38724107.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23229,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23413,11 @@
           <t>25.59</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>25.94</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23464,16 @@
           <t>28327621.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>64293510.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>64293510</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>53134957.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>197699079.6</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>197699079.6</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23490,10 @@
           <t>-13938079.56667101</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>28327621</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>28327621.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23659,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23843,11 @@
           <t>25.52</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>25.88</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23894,16 @@
           <t>32929925.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>66663290.6</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>66663290.6</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>54706545.9</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>197755621.26</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>197755621.26</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23920,10 @@
           <t>-13082493.16375375</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>32929925</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>32929925.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24089,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24273,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24324,16 @@
           <t>37828336.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>70079408.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>70079408.40000001</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>58159640.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>197616845.6</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>197616845.6</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24350,10 @@
           <t>-11886098.97516645</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>37828336</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>37828336.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24519,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24703,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24754,16 @@
           <t>78997267.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>68268779.4</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>68268779.40000001</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>64193506.3</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>197596036.22</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>197596036.22</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>-10277290.63521439</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>78997267</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>78997267.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
